--- a/CDF_Demand_Variation/SplineCDF_Fall2025_Demand Variation.xlsx
+++ b/CDF_Demand_Variation/SplineCDF_Fall2025_Demand Variation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Demand_Variation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3678CF1B-5C46-4746-8E1F-F719BC55AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{3678CF1B-5C46-4746-8E1F-F719BC55AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F996F6B-794E-425E-B520-08B216A18F68}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6499,103 +6499,103 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>0.249223497878273</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.11</v>
+        <v>5.9935338970198336E-2</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>9.9999999999999992E-2</v>
+        <v>0.05</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.11</v>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-3.5714285714285587E-3</v>
+        <v>-3.3846153846153859E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>3.2142857142856973E-2</v>
+        <v>8.7692307692307708E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.17142857142857154</v>
+        <v>4.6153846153846149E-2</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-0.19999999999999996</v>
+        <v>-9.9223497878273004E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>1.1666666666666656</v>
+        <v>2.1498424540292485</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.98481705003444098</v>
+        <v>0.83262862918046421</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.98481705003444098</v>
+        <v>0.83262862918046421</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-75.000000000000114</v>
+        <v>-3.6012396694214859</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-141.99999999999989</v>
+        <v>0.46560034114431736</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>-10584.00000000008</v>
+        <v>-1.6755898193311822</v>
       </c>
       <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>125.00000000000028</v>
+        <v>1.3152131913684597</v>
       </c>
       <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>5.0000000000000027</v>
+        <v>1.095633708472177</v>
       </c>
       <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>0.96672256442390625</v>
+        <v>1.7487395543788551</v>
       </c>
       <c r="S2">
         <f ca="1">-Q2</f>
-        <v>-5.0000000000000027</v>
+        <v>-1.095633708472177</v>
       </c>
       <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>0.94852813742385678</v>
+        <v>0.83486260779595889</v>
       </c>
       <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>0.54852813742385809</v>
+        <v>0.95342187845276183</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>2.9999999999999947</v>
+        <v>0.86363636363636342</v>
       </c>
       <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>12.485281374238568</v>
+        <v>2.6930435937248416</v>
       </c>
       <c r="X2">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-4.4852813742385838</v>
+        <v>-1.0956683998355845</v>
       </c>
       <c r="Y2">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>1.0000000000000002</v>
+        <v>0.99353389701983297</v>
       </c>
       <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>1.0000000000000002</v>
+        <v>0.99353389701983297</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36453,15 +36453,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36599,6 +36590,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36606,14 +36606,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE2023E-0921-4393-91FB-46E0A00982C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{433CC6CD-0720-416A-9285-478ED49A8EEA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36631,6 +36623,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE2023E-0921-4393-91FB-46E0A00982C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE64786-30B5-45F8-B034-D1FDB650E7A7}">
   <ds:schemaRefs>

--- a/CDF_Demand_Variation/SplineCDF_Fall2025_Demand Variation.xlsx
+++ b/CDF_Demand_Variation/SplineCDF_Fall2025_Demand Variation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Demand_Variation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{3678CF1B-5C46-4746-8E1F-F719BC55AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F996F6B-794E-425E-B520-08B216A18F68}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{3678CF1B-5C46-4746-8E1F-F719BC55AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE2F5BB9-3BFF-47C0-9F12-7E2399095779}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4749,6 +4749,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6499,103 +6503,103 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.249223497878273</v>
+        <v>0.95532292568571797</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>5.9935338970198336E-2</v>
+        <v>0.10797393755683463</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.05</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>6.0000000000000005E-2</v>
+        <v>0.11</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-3.3846153846153859E-2</v>
+        <v>-3.5714285714285587E-3</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>8.7692307692307708E-2</v>
+        <v>3.2142857142856973E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>4.6153846153846149E-2</v>
+        <v>0.17142857142857154</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-9.9223497878273004E-2</v>
+        <v>-0.15532292568571793</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>2.1498424540292485</v>
+        <v>0.906050399833354</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.83262862918046421</v>
+        <v>0.78925287959339319</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.83262862918046421</v>
+        <v>0.78925287959339319</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-3.6012396694214859</v>
+        <v>-75.000000000000114</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>0.46560034114431736</v>
+        <v>-154.50958080799887</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>-1.6755898193311822</v>
+        <v>-9656.6973596341886</v>
       </c>
       <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>1.3152131913684597</v>
+        <v>125.00000000000028</v>
       </c>
       <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>1.095633708472177</v>
+        <v>5.0000000000000027</v>
       </c>
       <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>1.7487395543788551</v>
+        <v>0.90455138074403141</v>
       </c>
       <c r="S2">
         <f ca="1">-Q2</f>
-        <v>-1.095633708472177</v>
+        <v>-5.0000000000000027</v>
       </c>
       <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>0.83486260779595889</v>
+        <v>0.95488704820183434</v>
       </c>
       <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>0.95342187845276183</v>
+        <v>0.51436579933852822</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>0.86363636363636342</v>
+        <v>2.9999999999999947</v>
       </c>
       <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>2.6930435937248416</v>
+        <v>12.548870482018343</v>
       </c>
       <c r="X2">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-1.0956683998355845</v>
+        <v>-4.3462642377018224</v>
       </c>
       <c r="Y2">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>0.99353389701983297</v>
+        <v>0.79739375568346293</v>
       </c>
       <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
@@ -6619,7 +6623,7 @@
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.99353389701983297</v>
+        <v>0.79739375568346293</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36453,6 +36457,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36590,15 +36603,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36606,6 +36610,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE2023E-0921-4393-91FB-46E0A00982C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{433CC6CD-0720-416A-9285-478ED49A8EEA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36623,14 +36635,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE2023E-0921-4393-91FB-46E0A00982C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE64786-30B5-45F8-B034-D1FDB650E7A7}">
   <ds:schemaRefs>

--- a/CDF_Demand_Variation/SplineCDF_Fall2025_Demand Variation.xlsx
+++ b/CDF_Demand_Variation/SplineCDF_Fall2025_Demand Variation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Demand_Variation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{3678CF1B-5C46-4746-8E1F-F719BC55AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE2F5BB9-3BFF-47C0-9F12-7E2399095779}"/>
+  <xr:revisionPtr revIDLastSave="1354" documentId="13_ncr:1_{3678CF1B-5C46-4746-8E1F-F719BC55AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71B7C4A3-8330-4DB7-9D3E-FE53B47FEB51}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6503,103 +6503,103 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.95532292568571797</v>
+        <v>0.53488978329663905</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.10797393755683463</v>
+        <v>8.2611095832066814E-2</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>9.9999999999999992E-2</v>
+        <v>0.08</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-3.5714285714285587E-3</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>3.2142857142856973E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.17142857142857154</v>
+        <v>0.12</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-0.15532292568571793</v>
+        <v>-3.4889783296639054E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.906050399833354</v>
+        <v>0.29074819413865882</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.78925287959339319</v>
+        <v>0.2575755994282482</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.78925287959339319</v>
+        <v>0.2575755994282482</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-75.000000000000114</v>
+        <v>-5.3333333333333295</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-154.50958080799887</v>
+        <v>-2.0962664827046229</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>-9656.6973596341886</v>
+        <v>-4.5200724011020519</v>
       </c>
       <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>125.00000000000028</v>
+        <v>2.370370370370368</v>
       </c>
       <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>5.0000000000000027</v>
+        <v>1.3333333333333328</v>
       </c>
       <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>0.90455138074403141</v>
+        <v>1.11276723214635</v>
       </c>
       <c r="S2">
         <f ca="1">-Q2</f>
-        <v>-5.0000000000000027</v>
+        <v>-1.3333333333333328</v>
       </c>
       <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>0.95488704820183434</v>
+        <v>0.93199339107263512</v>
       </c>
       <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>0.51436579933852822</v>
+        <v>0.62782557847764575</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>2.9999999999999947</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>12.548870482018343</v>
+        <v>3.1519823761936925</v>
       </c>
       <c r="X2">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-4.3462642377018224</v>
+        <v>-1.4130919594003739</v>
       </c>
       <c r="Y2">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>0.79739375568346293</v>
+        <v>0.26110958320668098</v>
       </c>
       <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.79739375568346293</v>
+        <v>0.26110958320668098</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36457,12 +36457,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36604,15 +36601,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE2023E-0921-4393-91FB-46E0A00982C1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE64786-30B5-45F8-B034-D1FDB650E7A7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -36636,10 +36637,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE64786-30B5-45F8-B034-D1FDB650E7A7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE2023E-0921-4393-91FB-46E0A00982C1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>